--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC42D23-2364-43EF-B257-D0BFAC6D4642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2776904E-A98F-4293-A683-E3710FC8DC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2776904E-A98F-4293-A683-E3710FC8DC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7DD838-1CFB-473A-9D15-4CFA046372E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7DD838-1CFB-473A-9D15-4CFA046372E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1621BF-91C4-497C-A892-2966191F529F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1621BF-91C4-497C-A892-2966191F529F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB344216-8DE5-4F2E-808D-71E182ED5760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB344216-8DE5-4F2E-808D-71E182ED5760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476E14ED-D025-419A-9E9B-E7471CF470E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1365,6 +1365,50 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>46321</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>114349</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>147660</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AEDBF92-4CEE-E7BD-89AD-CF8C7CD134FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11191875" y="7628221"/>
+          <a:ext cx="4567287" cy="2139689"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -6281,7 +6325,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0</v>
+        <v>23.967360000000003</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -6783,31 +6827,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>0</v>
+        <v>23.967360000000003</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>0</v>
+        <v>22.768992000000001</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>0</v>
+        <v>21.570624000000002</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>0</v>
+        <v>47.695046400000003</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>31.397241600000005</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>31.397241600000005</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>25.165728000000005</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -7203,39 +7247,35 @@
       </c>
       <c r="D47">
         <f t="shared" ref="D47:J50" si="9">AVERAGE($M47:$N47)*D39</f>
-        <v>13.700000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="E47">
         <f t="shared" si="9"/>
-        <v>14.111000000000001</v>
+        <v>11.124000000000001</v>
       </c>
       <c r="F47">
         <f t="shared" si="9"/>
-        <v>15.481</v>
+        <v>12.203999999999999</v>
       </c>
       <c r="G47">
         <f t="shared" si="9"/>
-        <v>15.891999999999999</v>
+        <v>12.528</v>
       </c>
       <c r="H47">
         <f t="shared" si="9"/>
-        <v>16.303000000000001</v>
+        <v>12.852</v>
       </c>
       <c r="I47">
         <f t="shared" si="9"/>
-        <v>17.399000000000001</v>
+        <v>13.716000000000001</v>
       </c>
       <c r="J47">
         <f t="shared" si="9"/>
-        <v>17.947000000000003</v>
+        <v>14.148000000000001</v>
       </c>
       <c r="M47">
-        <f>HLOOKUP($B47&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>10.3</v>
-      </c>
-      <c r="N47">
-        <f>HLOOKUP($B47&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>17.100000000000001</v>
+        <f>3*3.6</f>
+        <v>10.8</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.45">
@@ -7248,39 +7288,35 @@
       </c>
       <c r="D48">
         <f t="shared" si="9"/>
-        <v>9.1499999999999986</v>
+        <v>7.2</v>
       </c>
       <c r="E48">
         <f t="shared" si="9"/>
-        <v>9.4244999999999983</v>
+        <v>7.4160000000000004</v>
       </c>
       <c r="F48">
         <f t="shared" si="9"/>
-        <v>9.9734999999999996</v>
+        <v>7.8480000000000008</v>
       </c>
       <c r="G48">
         <f t="shared" si="9"/>
-        <v>10.796999999999997</v>
+        <v>8.4960000000000004</v>
       </c>
       <c r="H48">
         <f t="shared" si="9"/>
-        <v>11.620499999999998</v>
+        <v>9.1440000000000001</v>
       </c>
       <c r="I48">
         <f t="shared" si="9"/>
-        <v>12.352499999999999</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="J48">
         <f t="shared" si="9"/>
-        <v>12.901499999999997</v>
+        <v>10.151999999999999</v>
       </c>
       <c r="M48">
-        <f>HLOOKUP($B48&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>7.6</v>
-      </c>
-      <c r="N48">
-        <f>HLOOKUP($B48&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>10.7</v>
+        <f>2*3.6</f>
+        <v>7.2</v>
       </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.45">
@@ -7833,7 +7869,8 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <f>3.42*0.8*8.76</f>
+        <v>23.967360000000003</v>
       </c>
       <c r="M18">
         <v>0</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476E14ED-D025-419A-9E9B-E7471CF470E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967BBD43-3EE2-4A9F-8258-AFA3062868C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1365,50 +1365,6 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>80962</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>46321</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>114349</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>147660</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AEDBF92-4CEE-E7BD-89AD-CF8C7CD134FC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11191875" y="7628221"/>
-          <a:ext cx="4567287" cy="2139689"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -6325,7 +6281,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>23.967360000000003</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -6827,31 +6783,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>23.967360000000003</v>
+        <v>0</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>22.768992000000001</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>21.570624000000002</v>
+        <v>0</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>47.695046400000003</v>
+        <v>0</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>31.397241600000005</v>
+        <v>0</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>31.397241600000005</v>
+        <v>0</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>25.165728000000005</v>
+        <v>0</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -7247,35 +7203,39 @@
       </c>
       <c r="D47">
         <f t="shared" ref="D47:J50" si="9">AVERAGE($M47:$N47)*D39</f>
-        <v>10.8</v>
+        <v>13.700000000000001</v>
       </c>
       <c r="E47">
         <f t="shared" si="9"/>
-        <v>11.124000000000001</v>
+        <v>14.111000000000001</v>
       </c>
       <c r="F47">
         <f t="shared" si="9"/>
-        <v>12.203999999999999</v>
+        <v>15.481</v>
       </c>
       <c r="G47">
         <f t="shared" si="9"/>
-        <v>12.528</v>
+        <v>15.891999999999999</v>
       </c>
       <c r="H47">
         <f t="shared" si="9"/>
-        <v>12.852</v>
+        <v>16.303000000000001</v>
       </c>
       <c r="I47">
         <f t="shared" si="9"/>
-        <v>13.716000000000001</v>
+        <v>17.399000000000001</v>
       </c>
       <c r="J47">
         <f t="shared" si="9"/>
-        <v>14.148000000000001</v>
+        <v>17.947000000000003</v>
       </c>
       <c r="M47">
-        <f>3*3.6</f>
-        <v>10.8</v>
+        <f>HLOOKUP($B47&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>10.3</v>
+      </c>
+      <c r="N47">
+        <f>HLOOKUP($B47&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>17.100000000000001</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.45">
@@ -7288,35 +7248,39 @@
       </c>
       <c r="D48">
         <f t="shared" si="9"/>
-        <v>7.2</v>
+        <v>9.1499999999999986</v>
       </c>
       <c r="E48">
         <f t="shared" si="9"/>
-        <v>7.4160000000000004</v>
+        <v>9.4244999999999983</v>
       </c>
       <c r="F48">
         <f t="shared" si="9"/>
-        <v>7.8480000000000008</v>
+        <v>9.9734999999999996</v>
       </c>
       <c r="G48">
         <f t="shared" si="9"/>
-        <v>8.4960000000000004</v>
+        <v>10.796999999999997</v>
       </c>
       <c r="H48">
         <f t="shared" si="9"/>
-        <v>9.1440000000000001</v>
+        <v>11.620499999999998</v>
       </c>
       <c r="I48">
         <f t="shared" si="9"/>
-        <v>9.7200000000000006</v>
+        <v>12.352499999999999</v>
       </c>
       <c r="J48">
         <f t="shared" si="9"/>
-        <v>10.151999999999999</v>
+        <v>12.901499999999997</v>
       </c>
       <c r="M48">
-        <f>2*3.6</f>
-        <v>7.2</v>
+        <f>HLOOKUP($B48&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>7.6</v>
+      </c>
+      <c r="N48">
+        <f>HLOOKUP($B48&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>10.7</v>
       </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.45">
@@ -7869,8 +7833,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <f>3.42*0.8*8.76</f>
-        <v>23.967360000000003</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>0</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967BBD43-3EE2-4A9F-8258-AFA3062868C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1475B6-CAB7-419A-B7FA-7327B8E6CF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1475B6-CAB7-419A-B7FA-7327B8E6CF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6627099B-74B5-4561-A670-596C7349B92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6627099B-74B5-4561-A670-596C7349B92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CD5D9B-E235-497A-9C9D-B77DCF9FF5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CD5D9B-E235-497A-9C9D-B77DCF9FF5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F7BF6B-5190-4717-B605-CCFC775F759A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F7BF6B-5190-4717-B605-CCFC775F759A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C049D1-F0BF-4306-947C-64D4DBA02BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="110">
   <si>
     <t>C1</t>
   </si>
@@ -396,6 +396,18 @@
   </si>
   <si>
     <t>Major LNG exporter, cheap domestic coal</t>
+  </si>
+  <si>
+    <t>CAGR</t>
+  </si>
+  <si>
+    <t>Slower Growth</t>
+  </si>
+  <si>
+    <t>Step Change</t>
+  </si>
+  <si>
+    <t>Accelerated</t>
   </si>
 </sst>
 </file>
@@ -860,22 +872,22 @@
                   <c:v>270.82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>270.82</c:v>
+                  <c:v>276.2364</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>270.82</c:v>
+                  <c:v>301.15183999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>276.2364</c:v>
+                  <c:v>327.96302000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>292.48560000000003</c:v>
+                  <c:v>357.48239999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>311.44299999999998</c:v>
+                  <c:v>389.43915999999996</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>349.3578</c:v>
+                  <c:v>424.37493999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6233,6 +6245,30 @@
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.45">
+      <c r="C9">
+        <v>2022</v>
+      </c>
+      <c r="D9">
+        <v>2025</v>
+      </c>
+      <c r="E9">
+        <v>2030</v>
+      </c>
+      <c r="F9">
+        <v>2035</v>
+      </c>
+      <c r="G9">
+        <v>2040</v>
+      </c>
+      <c r="H9">
+        <v>2045</v>
+      </c>
+      <c r="I9">
+        <v>2050</v>
+      </c>
+      <c r="J9" t="s">
+        <v>106</v>
+      </c>
       <c r="N9" t="s">
         <v>4</v>
       </c>
@@ -6247,6 +6283,36 @@
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1.02</v>
+      </c>
+      <c r="E10">
+        <v>1.1120000000000001</v>
+      </c>
+      <c r="F10">
+        <v>1.2110000000000001</v>
+      </c>
+      <c r="G10">
+        <v>1.32</v>
+      </c>
+      <c r="H10">
+        <v>1.4379999999999999</v>
+      </c>
+      <c r="I10">
+        <v>1.5669999999999999</v>
+      </c>
+      <c r="J10">
+        <v>1.7299999999999999E-2</v>
+      </c>
       <c r="N10" s="1">
         <v>2022</v>
       </c>
@@ -6261,6 +6327,33 @@
       </c>
     </row>
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1.02</v>
+      </c>
+      <c r="E11">
+        <v>1.159</v>
+      </c>
+      <c r="F11">
+        <v>1.3180000000000001</v>
+      </c>
+      <c r="G11">
+        <v>1.498</v>
+      </c>
+      <c r="H11">
+        <v>1.7030000000000001</v>
+      </c>
+      <c r="I11">
+        <v>1.9359999999999999</v>
+      </c>
+      <c r="J11">
+        <v>2.5999999999999999E-2</v>
+      </c>
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
         <v>270.82</v>
@@ -6279,9 +6372,39 @@
       </c>
     </row>
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1.02</v>
+      </c>
+      <c r="E12">
+        <v>1.1990000000000001</v>
+      </c>
+      <c r="F12">
+        <v>1.411</v>
+      </c>
+      <c r="G12">
+        <v>1.659</v>
+      </c>
+      <c r="H12">
+        <v>1.9510000000000001</v>
+      </c>
+      <c r="I12">
+        <v>2.294</v>
+      </c>
+      <c r="J12">
+        <v>3.2899999999999999E-2</v>
+      </c>
       <c r="N12" s="17">
-        <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0</v>
+        <f>3.27*0.8*8.76</f>
+        <v>22.916160000000001</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -6294,10 +6417,7 @@
       </c>
     </row>
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N13" s="17">
-        <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0</v>
-      </c>
+      <c r="N13" s="17"/>
       <c r="AF13" t="s">
         <v>9</v>
       </c>
@@ -6314,64 +6434,64 @@
         <v>11</v>
       </c>
       <c r="C15" s="3" t="str">
-        <f>VLOOKUP(controller!$D$5,$I$3:$J$5,2,FALSE)</f>
-        <v>C4</v>
+        <f>controller!$D$5</f>
+        <v>base</v>
       </c>
       <c r="D15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <f>SUMIF($A$10:$A$12,$C$15,C$10:C$12)</f>
         <v>1</v>
       </c>
       <c r="E15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
+        <f t="shared" ref="E15:J15" si="0">SUMIF($A$10:$A$12,$C$15,D$10:D$12)</f>
+        <v>1.02</v>
       </c>
       <c r="F15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>1.1120000000000001</v>
       </c>
       <c r="G15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.02</v>
+        <f t="shared" si="0"/>
+        <v>1.2110000000000001</v>
       </c>
       <c r="H15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.08</v>
+        <f t="shared" si="0"/>
+        <v>1.32</v>
       </c>
       <c r="I15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.1499999999999999</v>
+        <f t="shared" si="0"/>
+        <v>1.4379999999999999</v>
       </c>
       <c r="J15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.29</v>
+        <f>SUMIF($A$10:$A$12,$C$15,I$10:I$12)</f>
+        <v>1.5669999999999999</v>
       </c>
       <c r="O15" s="8">
         <f>N11</f>
         <v>270.82</v>
       </c>
       <c r="P15" s="8">
-        <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>270.82</v>
+        <f t="shared" ref="P15:U15" si="1">$N$11*E15</f>
+        <v>276.2364</v>
       </c>
       <c r="Q15" s="8">
-        <f t="shared" si="0"/>
-        <v>270.82</v>
+        <f t="shared" si="1"/>
+        <v>301.15183999999999</v>
       </c>
       <c r="R15" s="8">
-        <f t="shared" si="0"/>
-        <v>276.2364</v>
+        <f t="shared" si="1"/>
+        <v>327.96302000000003</v>
       </c>
       <c r="S15" s="8">
-        <f t="shared" si="0"/>
-        <v>292.48560000000003</v>
+        <f t="shared" si="1"/>
+        <v>357.48239999999998</v>
       </c>
       <c r="T15" s="8">
-        <f t="shared" si="0"/>
-        <v>311.44299999999998</v>
+        <f t="shared" si="1"/>
+        <v>389.43915999999996</v>
       </c>
       <c r="U15" s="8">
-        <f t="shared" si="0"/>
-        <v>349.3578</v>
+        <f t="shared" si="1"/>
+        <v>424.37493999999998</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -6379,32 +6499,25 @@
         <v>93</v>
       </c>
       <c r="D16" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1</v>
       </c>
       <c r="E16" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F16" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G16" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.99</v>
+        <v>1</v>
       </c>
       <c r="H16" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="I16" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="J16" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -6418,27 +6531,27 @@
         <v>2020</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" ref="E18:J18" si="1">P18</f>
+        <f t="shared" ref="E18:J18" si="2">P18</f>
         <v>2025</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2030</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2035</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2040</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2045</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2050</v>
       </c>
       <c r="N18" s="4" t="s">
@@ -6505,31 +6618,31 @@
         <v>15</v>
       </c>
       <c r="O19" s="6">
-        <f t="shared" ref="O19:U21" si="2">D19*O$15</f>
+        <f t="shared" ref="O19:U21" si="3">D19*O$15</f>
         <v>0</v>
       </c>
       <c r="P19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V19" t="s">
@@ -6543,62 +6656,62 @@
       </c>
       <c r="D20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="E20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="F20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="G20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="I20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="J20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>18</v>
       </c>
       <c r="O20" s="6">
-        <f t="shared" si="2"/>
-        <v>92.078800000000001</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="P20" s="6">
-        <f t="shared" si="2"/>
-        <v>86.662400000000005</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" si="2"/>
-        <v>83.9542</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="R20" s="6">
-        <f t="shared" si="2"/>
-        <v>82.870919999999998</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="S20" s="6">
-        <f t="shared" si="2"/>
-        <v>81.895968000000011</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="T20" s="6">
-        <f t="shared" si="2"/>
-        <v>90.318469999999991</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="U20" s="6">
-        <f t="shared" si="2"/>
-        <v>97.820184000000012</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -6610,62 +6723,62 @@
       </c>
       <c r="D21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="E21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="F21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="G21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="H21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="I21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="J21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>21</v>
       </c>
       <c r="O21" s="6">
-        <f t="shared" si="2"/>
-        <v>170.61660000000001</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="P21" s="6">
-        <f t="shared" si="2"/>
-        <v>176.03300000000002</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="2"/>
-        <v>176.03300000000002</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="R21" s="6">
-        <f t="shared" si="2"/>
-        <v>179.55366000000001</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="S21" s="6">
-        <f t="shared" si="2"/>
-        <v>187.19078400000004</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="T21" s="6">
-        <f t="shared" si="2"/>
-        <v>193.09465999999998</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="U21" s="6">
-        <f t="shared" si="2"/>
-        <v>209.61467999999999</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -6677,62 +6790,62 @@
       </c>
       <c r="D22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="J22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N22" s="10" t="s">
         <v>23</v>
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>5.4164000000000003</v>
+        <v>0</v>
       </c>
       <c r="P22" s="6">
-        <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>5.4164000000000003</v>
+        <f t="shared" ref="P22:U22" si="4">O22</f>
+        <v>0</v>
       </c>
       <c r="Q22" s="6">
-        <f t="shared" si="3"/>
-        <v>5.4164000000000003</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="R22" s="6">
-        <f t="shared" si="3"/>
-        <v>5.4164000000000003</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="S22" s="6">
-        <f t="shared" si="3"/>
-        <v>5.4164000000000003</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="T22" s="6">
-        <f t="shared" si="3"/>
-        <v>5.4164000000000003</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" si="3"/>
-        <v>5.4164000000000003</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -6746,32 +6859,32 @@
         <v>24</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>2.7081999999999766</v>
+        <f t="shared" ref="O23:U23" si="5">O15-SUM(O20:O22)</f>
+        <v>270.82</v>
       </c>
       <c r="P23" s="6">
-        <f t="shared" si="4"/>
-        <v>2.7081999999999766</v>
+        <f t="shared" si="5"/>
+        <v>276.2364</v>
       </c>
       <c r="Q23" s="6">
-        <f t="shared" si="4"/>
-        <v>5.4163999999999533</v>
+        <f t="shared" si="5"/>
+        <v>301.15183999999999</v>
       </c>
       <c r="R23" s="6">
-        <f t="shared" si="4"/>
-        <v>8.3954200000000014</v>
+        <f t="shared" si="5"/>
+        <v>327.96302000000003</v>
       </c>
       <c r="S23" s="6">
-        <f t="shared" si="4"/>
-        <v>17.982447999999977</v>
+        <f t="shared" si="5"/>
+        <v>357.48239999999998</v>
       </c>
       <c r="T23" s="6">
-        <f t="shared" si="4"/>
-        <v>22.613470000000007</v>
+        <f t="shared" si="5"/>
+        <v>389.43915999999996</v>
       </c>
       <c r="U23" s="6">
-        <f t="shared" si="4"/>
-        <v>36.506535999999983</v>
+        <f t="shared" si="5"/>
+        <v>424.37493999999998</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -6783,31 +6896,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>0</v>
+        <v>22.916160000000001</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>0</v>
+        <v>22.916160000000001</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>0</v>
+        <v>22.916160000000001</v>
       </c>
       <c r="R24" s="20">
-        <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>0</v>
+        <f t="shared" ref="R24:U24" si="6">$N$12*G16</f>
+        <v>22.916160000000001</v>
       </c>
       <c r="S24" s="20">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>22.916160000000001</v>
       </c>
       <c r="T24" s="20">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>22.916160000000001</v>
       </c>
       <c r="U24" s="20">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>22.916160000000001</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -6826,23 +6939,23 @@
         <v>0</v>
       </c>
       <c r="Q25" s="20">
-        <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
+        <f t="shared" ref="Q25:U25" si="7">$N$13*F16</f>
         <v>0</v>
       </c>
       <c r="R25" s="20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S25" s="20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T25" s="20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U25" s="20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V25" s="18" t="s">
@@ -6926,31 +7039,31 @@
         <v>28</v>
       </c>
       <c r="O29" s="4">
-        <f t="shared" ref="O29:U29" si="7">O18</f>
+        <f t="shared" ref="O29:U29" si="8">O18</f>
         <v>2022</v>
       </c>
       <c r="P29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2025</v>
       </c>
       <c r="Q29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2030</v>
       </c>
       <c r="R29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2035</v>
       </c>
       <c r="S29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2040</v>
       </c>
       <c r="T29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2045</v>
       </c>
       <c r="U29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2050</v>
       </c>
       <c r="V29" s="4" t="s">
@@ -7167,23 +7280,23 @@
         <v>2025</v>
       </c>
       <c r="F46">
-        <f t="shared" ref="F46:J46" si="8">F18</f>
+        <f t="shared" ref="F46:J46" si="9">F18</f>
         <v>2030</v>
       </c>
       <c r="G46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2035</v>
       </c>
       <c r="H46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2040</v>
       </c>
       <c r="I46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2045</v>
       </c>
       <c r="J46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2050</v>
       </c>
       <c r="M46" t="s">
@@ -7202,31 +7315,31 @@
         <v>Gas</v>
       </c>
       <c r="D47">
-        <f t="shared" ref="D47:J50" si="9">AVERAGE($M47:$N47)*D39</f>
+        <f t="shared" ref="D47:J50" si="10">AVERAGE($M47:$N47)*D39</f>
         <v>13.700000000000001</v>
       </c>
       <c r="E47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14.111000000000001</v>
       </c>
       <c r="F47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>15.481</v>
       </c>
       <c r="G47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>15.891999999999999</v>
       </c>
       <c r="H47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>16.303000000000001</v>
       </c>
       <c r="I47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>17.399000000000001</v>
       </c>
       <c r="J47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>17.947000000000003</v>
       </c>
       <c r="M47">
@@ -7243,35 +7356,35 @@
         <v>77</v>
       </c>
       <c r="C48" t="str">
-        <f t="shared" ref="C48:C50" si="10">B48</f>
+        <f t="shared" ref="C48:C50" si="11">B48</f>
         <v>Coal</v>
       </c>
       <c r="D48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.1499999999999986</v>
       </c>
       <c r="E48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.4244999999999983</v>
       </c>
       <c r="F48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.9734999999999996</v>
       </c>
       <c r="G48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10.796999999999997</v>
       </c>
       <c r="H48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11.620499999999998</v>
       </c>
       <c r="I48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12.352499999999999</v>
       </c>
       <c r="J48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12.901499999999997</v>
       </c>
       <c r="M48">
@@ -7288,35 +7401,35 @@
         <v>78</v>
       </c>
       <c r="C49" t="str">
+        <f t="shared" si="11"/>
+        <v>Oil</v>
+      </c>
+      <c r="D49">
         <f t="shared" si="10"/>
-        <v>Oil</v>
-      </c>
-      <c r="D49">
-        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="E49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>55.120000000000005</v>
       </c>
       <c r="F49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>55.650000000000006</v>
       </c>
       <c r="G49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>55.120000000000005</v>
       </c>
       <c r="H49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>55.120000000000005</v>
       </c>
       <c r="I49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>62.01</v>
       </c>
       <c r="J49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>66.25</v>
       </c>
       <c r="M49">
@@ -7333,16 +7446,16 @@
         <v>79</v>
       </c>
       <c r="C50" t="str">
+        <f t="shared" si="11"/>
+        <v>Bioenergy</v>
+      </c>
+      <c r="D50">
         <f t="shared" si="10"/>
-        <v>Bioenergy</v>
-      </c>
-      <c r="D50">
-        <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="J50">
+      <c r="J50" t="e">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>72</v>
+        <v>#N/A</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C049D1-F0BF-4306-947C-64D4DBA02BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BF3D39-907A-4D12-BC0A-311929D64FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="106">
   <si>
     <t>C1</t>
   </si>
@@ -396,18 +396,6 @@
   </si>
   <si>
     <t>Major LNG exporter, cheap domestic coal</t>
-  </si>
-  <si>
-    <t>CAGR</t>
-  </si>
-  <si>
-    <t>Slower Growth</t>
-  </si>
-  <si>
-    <t>Step Change</t>
-  </si>
-  <si>
-    <t>Accelerated</t>
   </si>
 </sst>
 </file>
@@ -872,22 +860,22 @@
                   <c:v>270.82</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>270.82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>270.82</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>276.2364</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>301.15183999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>327.96302000000003</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>357.48239999999998</c:v>
+                  <c:v>292.48560000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>389.43915999999996</c:v>
+                  <c:v>311.44299999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>424.37493999999998</c:v>
+                  <c:v>349.3578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6245,30 +6233,6 @@
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="C9">
-        <v>2022</v>
-      </c>
-      <c r="D9">
-        <v>2025</v>
-      </c>
-      <c r="E9">
-        <v>2030</v>
-      </c>
-      <c r="F9">
-        <v>2035</v>
-      </c>
-      <c r="G9">
-        <v>2040</v>
-      </c>
-      <c r="H9">
-        <v>2045</v>
-      </c>
-      <c r="I9">
-        <v>2050</v>
-      </c>
-      <c r="J9" t="s">
-        <v>106</v>
-      </c>
       <c r="N9" t="s">
         <v>4</v>
       </c>
@@ -6283,36 +6247,6 @@
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1.02</v>
-      </c>
-      <c r="E10">
-        <v>1.1120000000000001</v>
-      </c>
-      <c r="F10">
-        <v>1.2110000000000001</v>
-      </c>
-      <c r="G10">
-        <v>1.32</v>
-      </c>
-      <c r="H10">
-        <v>1.4379999999999999</v>
-      </c>
-      <c r="I10">
-        <v>1.5669999999999999</v>
-      </c>
-      <c r="J10">
-        <v>1.7299999999999999E-2</v>
-      </c>
       <c r="N10" s="1">
         <v>2022</v>
       </c>
@@ -6327,33 +6261,6 @@
       </c>
     </row>
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1.02</v>
-      </c>
-      <c r="E11">
-        <v>1.159</v>
-      </c>
-      <c r="F11">
-        <v>1.3180000000000001</v>
-      </c>
-      <c r="G11">
-        <v>1.498</v>
-      </c>
-      <c r="H11">
-        <v>1.7030000000000001</v>
-      </c>
-      <c r="I11">
-        <v>1.9359999999999999</v>
-      </c>
-      <c r="J11">
-        <v>2.5999999999999999E-2</v>
-      </c>
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
         <v>270.82</v>
@@ -6372,39 +6279,9 @@
       </c>
     </row>
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1.02</v>
-      </c>
-      <c r="E12">
-        <v>1.1990000000000001</v>
-      </c>
-      <c r="F12">
-        <v>1.411</v>
-      </c>
-      <c r="G12">
-        <v>1.659</v>
-      </c>
-      <c r="H12">
-        <v>1.9510000000000001</v>
-      </c>
-      <c r="I12">
-        <v>2.294</v>
-      </c>
-      <c r="J12">
-        <v>3.2899999999999999E-2</v>
-      </c>
       <c r="N12" s="17">
-        <f>3.27*0.8*8.76</f>
-        <v>22.916160000000001</v>
+        <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>0</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -6417,7 +6294,10 @@
       </c>
     </row>
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N13" s="17"/>
+      <c r="N13" s="17">
+        <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>0</v>
+      </c>
       <c r="AF13" t="s">
         <v>9</v>
       </c>
@@ -6434,64 +6314,64 @@
         <v>11</v>
       </c>
       <c r="C15" s="3" t="str">
-        <f>controller!$D$5</f>
-        <v>base</v>
+        <f>VLOOKUP(controller!$D$5,$I$3:$J$5,2,FALSE)</f>
+        <v>C4</v>
       </c>
       <c r="D15" s="11">
-        <f>SUMIF($A$10:$A$12,$C$15,C$10:C$12)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1</v>
       </c>
       <c r="E15" s="11">
-        <f t="shared" ref="E15:J15" si="0">SUMIF($A$10:$A$12,$C$15,D$10:D$12)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="F15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.02</v>
       </c>
-      <c r="F15" s="11">
-        <f t="shared" si="0"/>
-        <v>1.1120000000000001</v>
-      </c>
-      <c r="G15" s="11">
-        <f t="shared" si="0"/>
-        <v>1.2110000000000001</v>
-      </c>
       <c r="H15" s="11">
-        <f t="shared" si="0"/>
-        <v>1.32</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.08</v>
       </c>
       <c r="I15" s="11">
-        <f t="shared" si="0"/>
-        <v>1.4379999999999999</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J15" s="11">
-        <f>SUMIF($A$10:$A$12,$C$15,I$10:I$12)</f>
-        <v>1.5669999999999999</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.29</v>
       </c>
       <c r="O15" s="8">
         <f>N11</f>
         <v>270.82</v>
       </c>
       <c r="P15" s="8">
-        <f t="shared" ref="P15:U15" si="1">$N$11*E15</f>
+        <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
+        <v>270.82</v>
+      </c>
+      <c r="Q15" s="8">
+        <f t="shared" si="0"/>
+        <v>270.82</v>
+      </c>
+      <c r="R15" s="8">
+        <f t="shared" si="0"/>
         <v>276.2364</v>
       </c>
-      <c r="Q15" s="8">
-        <f t="shared" si="1"/>
-        <v>301.15183999999999</v>
-      </c>
-      <c r="R15" s="8">
-        <f t="shared" si="1"/>
-        <v>327.96302000000003</v>
-      </c>
       <c r="S15" s="8">
-        <f t="shared" si="1"/>
-        <v>357.48239999999998</v>
+        <f t="shared" si="0"/>
+        <v>292.48560000000003</v>
       </c>
       <c r="T15" s="8">
-        <f t="shared" si="1"/>
-        <v>389.43915999999996</v>
+        <f t="shared" si="0"/>
+        <v>311.44299999999998</v>
       </c>
       <c r="U15" s="8">
-        <f t="shared" si="1"/>
-        <v>424.37493999999998</v>
+        <f t="shared" si="0"/>
+        <v>349.3578</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -6499,25 +6379,32 @@
         <v>93</v>
       </c>
       <c r="D16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1</v>
       </c>
       <c r="E16" s="11">
-        <v>1</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.95</v>
       </c>
       <c r="F16" s="11">
-        <v>1</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.9</v>
       </c>
       <c r="G16" s="11">
-        <v>1</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.99</v>
       </c>
       <c r="H16" s="11">
-        <v>1</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.31</v>
       </c>
       <c r="I16" s="11">
-        <v>1</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.31</v>
       </c>
       <c r="J16" s="11">
-        <v>1</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.05</v>
       </c>
     </row>
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -6531,27 +6418,27 @@
         <v>2020</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" ref="E18:J18" si="2">P18</f>
+        <f t="shared" ref="E18:J18" si="1">P18</f>
         <v>2025</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2030</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2035</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2040</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2045</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2050</v>
       </c>
       <c r="N18" s="4" t="s">
@@ -6618,31 +6505,31 @@
         <v>15</v>
       </c>
       <c r="O19" s="6">
-        <f t="shared" ref="O19:U21" si="3">D19*O$15</f>
+        <f t="shared" ref="O19:U21" si="2">D19*O$15</f>
         <v>0</v>
       </c>
       <c r="P19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V19" t="s">
@@ -6656,62 +6543,62 @@
       </c>
       <c r="D20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="E20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="F20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="G20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>18</v>
       </c>
       <c r="O20" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>92.078800000000001</v>
       </c>
       <c r="P20" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>86.662400000000005</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>83.9542</v>
       </c>
       <c r="R20" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>82.870919999999998</v>
       </c>
       <c r="S20" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>81.895968000000011</v>
       </c>
       <c r="T20" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>90.318469999999991</v>
       </c>
       <c r="U20" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>97.820184000000012</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -6723,62 +6610,62 @@
       </c>
       <c r="D21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="E21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="F21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="G21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="H21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="I21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="J21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>21</v>
       </c>
       <c r="O21" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>170.61660000000001</v>
       </c>
       <c r="P21" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>176.03300000000002</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>176.03300000000002</v>
       </c>
       <c r="R21" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>179.55366000000001</v>
       </c>
       <c r="S21" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>187.19078400000004</v>
       </c>
       <c r="T21" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>193.09465999999998</v>
       </c>
       <c r="U21" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>209.61467999999999</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -6790,62 +6677,62 @@
       </c>
       <c r="D22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J22" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N22" s="10" t="s">
         <v>23</v>
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>0</v>
+        <v>5.4164000000000003</v>
       </c>
       <c r="P22" s="6">
-        <f t="shared" ref="P22:U22" si="4">O22</f>
-        <v>0</v>
+        <f t="shared" ref="P22:U22" si="3">O22</f>
+        <v>5.4164000000000003</v>
       </c>
       <c r="Q22" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>5.4164000000000003</v>
       </c>
       <c r="R22" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>5.4164000000000003</v>
       </c>
       <c r="S22" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>5.4164000000000003</v>
       </c>
       <c r="T22" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>5.4164000000000003</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>5.4164000000000003</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -6859,32 +6746,32 @@
         <v>24</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" ref="O23:U23" si="5">O15-SUM(O20:O22)</f>
-        <v>270.82</v>
+        <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
+        <v>2.7081999999999766</v>
       </c>
       <c r="P23" s="6">
-        <f t="shared" si="5"/>
-        <v>276.2364</v>
+        <f t="shared" si="4"/>
+        <v>2.7081999999999766</v>
       </c>
       <c r="Q23" s="6">
-        <f t="shared" si="5"/>
-        <v>301.15183999999999</v>
+        <f t="shared" si="4"/>
+        <v>5.4163999999999533</v>
       </c>
       <c r="R23" s="6">
-        <f t="shared" si="5"/>
-        <v>327.96302000000003</v>
+        <f t="shared" si="4"/>
+        <v>8.3954200000000014</v>
       </c>
       <c r="S23" s="6">
-        <f t="shared" si="5"/>
-        <v>357.48239999999998</v>
+        <f t="shared" si="4"/>
+        <v>17.982447999999977</v>
       </c>
       <c r="T23" s="6">
-        <f t="shared" si="5"/>
-        <v>389.43915999999996</v>
+        <f t="shared" si="4"/>
+        <v>22.613470000000007</v>
       </c>
       <c r="U23" s="6">
-        <f t="shared" si="5"/>
-        <v>424.37493999999998</v>
+        <f t="shared" si="4"/>
+        <v>36.506535999999983</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -6896,31 +6783,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>22.916160000000001</v>
+        <v>0</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>22.916160000000001</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>22.916160000000001</v>
+        <v>0</v>
       </c>
       <c r="R24" s="20">
-        <f t="shared" ref="R24:U24" si="6">$N$12*G16</f>
-        <v>22.916160000000001</v>
+        <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
+        <v>0</v>
       </c>
       <c r="S24" s="20">
-        <f t="shared" si="6"/>
-        <v>22.916160000000001</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="T24" s="20">
-        <f t="shared" si="6"/>
-        <v>22.916160000000001</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="U24" s="20">
-        <f t="shared" si="6"/>
-        <v>22.916160000000001</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -6939,23 +6826,23 @@
         <v>0</v>
       </c>
       <c r="Q25" s="20">
-        <f t="shared" ref="Q25:U25" si="7">$N$13*F16</f>
+        <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
         <v>0</v>
       </c>
       <c r="R25" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S25" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T25" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U25" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V25" s="18" t="s">
@@ -7039,31 +6926,31 @@
         <v>28</v>
       </c>
       <c r="O29" s="4">
-        <f t="shared" ref="O29:U29" si="8">O18</f>
+        <f t="shared" ref="O29:U29" si="7">O18</f>
         <v>2022</v>
       </c>
       <c r="P29" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2025</v>
       </c>
       <c r="Q29" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2030</v>
       </c>
       <c r="R29" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2035</v>
       </c>
       <c r="S29" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2040</v>
       </c>
       <c r="T29" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2045</v>
       </c>
       <c r="U29" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2050</v>
       </c>
       <c r="V29" s="4" t="s">
@@ -7280,23 +7167,23 @@
         <v>2025</v>
       </c>
       <c r="F46">
-        <f t="shared" ref="F46:J46" si="9">F18</f>
+        <f t="shared" ref="F46:J46" si="8">F18</f>
         <v>2030</v>
       </c>
       <c r="G46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2035</v>
       </c>
       <c r="H46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2040</v>
       </c>
       <c r="I46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2045</v>
       </c>
       <c r="J46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2050</v>
       </c>
       <c r="M46" t="s">
@@ -7315,31 +7202,31 @@
         <v>Gas</v>
       </c>
       <c r="D47">
-        <f t="shared" ref="D47:J50" si="10">AVERAGE($M47:$N47)*D39</f>
+        <f t="shared" ref="D47:J50" si="9">AVERAGE($M47:$N47)*D39</f>
         <v>13.700000000000001</v>
       </c>
       <c r="E47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>14.111000000000001</v>
       </c>
       <c r="F47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>15.481</v>
       </c>
       <c r="G47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>15.891999999999999</v>
       </c>
       <c r="H47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>16.303000000000001</v>
       </c>
       <c r="I47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>17.399000000000001</v>
       </c>
       <c r="J47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>17.947000000000003</v>
       </c>
       <c r="M47">
@@ -7356,35 +7243,35 @@
         <v>77</v>
       </c>
       <c r="C48" t="str">
-        <f t="shared" ref="C48:C50" si="11">B48</f>
+        <f t="shared" ref="C48:C50" si="10">B48</f>
         <v>Coal</v>
       </c>
       <c r="D48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>9.1499999999999986</v>
       </c>
       <c r="E48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>9.4244999999999983</v>
       </c>
       <c r="F48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>9.9734999999999996</v>
       </c>
       <c r="G48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>10.796999999999997</v>
       </c>
       <c r="H48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>11.620499999999998</v>
       </c>
       <c r="I48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>12.352499999999999</v>
       </c>
       <c r="J48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>12.901499999999997</v>
       </c>
       <c r="M48">
@@ -7401,35 +7288,35 @@
         <v>78</v>
       </c>
       <c r="C49" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>Oil</v>
       </c>
       <c r="D49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="E49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>55.120000000000005</v>
       </c>
       <c r="F49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>55.650000000000006</v>
       </c>
       <c r="G49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>55.120000000000005</v>
       </c>
       <c r="H49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>55.120000000000005</v>
       </c>
       <c r="I49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>62.01</v>
       </c>
       <c r="J49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>66.25</v>
       </c>
       <c r="M49">
@@ -7446,16 +7333,16 @@
         <v>79</v>
       </c>
       <c r="C50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>Bioenergy</v>
       </c>
       <c r="D50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="J50" t="e">
+      <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>#N/A</v>
+        <v>72</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BF3D39-907A-4D12-BC0A-311929D64FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544E2D94-87DD-40CB-910D-84D65F749404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544E2D94-87DD-40CB-910D-84D65F749404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961DD434-ED76-4EB5-8EF1-8AA003828B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
